--- a/ZonasEscolares/excels/LIMA-LIMA-INDEPENDENCIA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-INDEPENDENCIA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-INDEPENDENCIA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-INDEPENDENCIA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.002377</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.05319299999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>456</v>
-      </c>
-      <c r="J2" t="n">
-        <v>27</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.002377</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.053193</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>MADRE TERESA DE CALCUTA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.999386</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.042867</v>
-      </c>
-      <c r="I3" t="n">
-        <v>17</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.999386</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.042867</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>0007 EL ERMITAÑO</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.9999</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.04992</v>
-      </c>
-      <c r="I4" t="n">
-        <v>319</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.9999</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.04992</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>09 J. WILLIAM FULBRIGHT / 3094-1 J. WILLIAM FULBRIGHT</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.979</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.04600000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1089</v>
-      </c>
-      <c r="J5" t="n">
-        <v>63</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.979</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.046</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>0055 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.99997</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.05406000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>324</v>
-      </c>
-      <c r="J6" t="n">
-        <v>16</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.99997</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.05406</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>0314</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.97145</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.04367999999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>231</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.97145</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.04368</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>0324 SAN JUDAS TADEO</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.9805</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.044</v>
-      </c>
-      <c r="I8" t="n">
-        <v>298</v>
-      </c>
-      <c r="J8" t="n">
-        <v>13</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.9805</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.044</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>0385 JOSE OLAYA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.96767</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.03917</v>
-      </c>
-      <c r="I9" t="n">
-        <v>248</v>
-      </c>
-      <c r="J9" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.96767</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.03917</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>0386 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.97702</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.05746000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>354</v>
-      </c>
-      <c r="J10" t="n">
-        <v>17</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.97702</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.05746</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>0390-1 EL ERMITAÑO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.99921</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.04472</v>
-      </c>
-      <c r="I11" t="n">
-        <v>229</v>
-      </c>
-      <c r="J11" t="n">
-        <v>11</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.99921</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.04472</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>0390-3 TAHUANTINSUYO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.9805</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.0403</v>
-      </c>
-      <c r="I12" t="n">
-        <v>344</v>
-      </c>
-      <c r="J12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.9805</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.0403</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>INDEPENDENCIA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.9975</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.05119999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1479</v>
-      </c>
-      <c r="J13" t="n">
-        <v>66</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.9975</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.0512</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>2044 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.9908</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.0534</v>
-      </c>
-      <c r="I14" t="n">
-        <v>389</v>
-      </c>
-      <c r="J14" t="n">
-        <v>22</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.9908</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.0534</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>2034 REPUBLICA DE IRLANDA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.99055</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.04115</v>
-      </c>
-      <c r="I15" t="n">
-        <v>439</v>
-      </c>
-      <c r="J15" t="n">
-        <v>21</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.99055</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.04115</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>2036 MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.99068</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.04604999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>474</v>
-      </c>
-      <c r="J16" t="n">
-        <v>21</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.99068</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.04605</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>2039 JORGE VICTOR CASTILLA MONTERO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.0003</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.0416</v>
-      </c>
-      <c r="I17" t="n">
-        <v>773</v>
-      </c>
-      <c r="J17" t="n">
-        <v>35</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.0003</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.0416</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>773</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>2041 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.96832</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.03948</v>
-      </c>
-      <c r="I18" t="n">
-        <v>845</v>
-      </c>
-      <c r="J18" t="n">
-        <v>47</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.96832</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.03948</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>2052 MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.97215</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.05</v>
-      </c>
-      <c r="I19" t="n">
-        <v>805</v>
-      </c>
-      <c r="J19" t="n">
-        <v>48</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.97215</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.05</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>2053 FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.9906</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.0498</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1388</v>
-      </c>
-      <c r="J20" t="n">
-        <v>67</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.9906</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.0498</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>2054 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.00723</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.04978</v>
-      </c>
-      <c r="I21" t="n">
-        <v>768</v>
-      </c>
-      <c r="J21" t="n">
-        <v>29</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.00723</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.04978</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>2056 JOSE GALVEZ</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.0062</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.0523</v>
-      </c>
-      <c r="I22" t="n">
-        <v>626</v>
-      </c>
-      <c r="J22" t="n">
-        <v>34</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.0062</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.0523</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>2057 JOSE GABRIEL CONDORCANQUI</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.9715</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.04559999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1843</v>
-      </c>
-      <c r="J23" t="n">
-        <v>87</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.9715</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.0456</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>2058 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-11.98001</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.04124</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1136</v>
-      </c>
-      <c r="J24" t="n">
-        <v>51</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-11.98001</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.04124</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>2061 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-11.991217</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.052363</v>
-      </c>
-      <c r="I25" t="n">
-        <v>969</v>
-      </c>
-      <c r="J25" t="n">
-        <v>46</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.991217</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.052363</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>3048 SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-11.979157</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.053748</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1239</v>
-      </c>
-      <c r="J26" t="n">
-        <v>71</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-11.979157</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.053748</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>3049 IMPERIO DEL TAHUANTINSUYO</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-11.9799</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.0367</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1515</v>
-      </c>
-      <c r="J27" t="n">
-        <v>106</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-11.9799</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.0367</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>3050 ALBERTO HURTADO ABADIA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-11.99422</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.05423</v>
-      </c>
-      <c r="I28" t="n">
-        <v>792</v>
-      </c>
-      <c r="J28" t="n">
-        <v>32</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-11.99422</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.05423</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>3051</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.00904</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.05034999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>573</v>
-      </c>
-      <c r="J29" t="n">
-        <v>24</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.00904</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.05035</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>3052</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.0048</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.0509</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1117</v>
-      </c>
-      <c r="J30" t="n">
-        <v>57</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.0048</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.0509</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>3053 VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.01675</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.04770000000001</v>
-      </c>
-      <c r="I31" t="n">
-        <v>235</v>
-      </c>
-      <c r="J31" t="n">
-        <v>12</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.01675</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.0477</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>3056 GRAN BRETAÑA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-11.98067</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.04073</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1568</v>
-      </c>
-      <c r="J32" t="n">
-        <v>74</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-11.98067</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.04073</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>3063 PATRICIA NATIVIDAD SANCHEZ</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-11.9989</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.0523</v>
-      </c>
-      <c r="I33" t="n">
-        <v>925</v>
-      </c>
-      <c r="J33" t="n">
-        <v>37</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-11.9989</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.0523</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>3094 RAMIRO PRIALE PRIALE</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-11.97711</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.05624</v>
-      </c>
-      <c r="I34" t="n">
-        <v>791</v>
-      </c>
-      <c r="J34" t="n">
-        <v>45</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-11.97711</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.05624</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>REPUBLICA DE COLOMBIA</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-11.98286</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.05382</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1640</v>
-      </c>
-      <c r="J35" t="n">
-        <v>89</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-11.98286</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.05382</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1640</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>LIBERTADOR SAN MARTIN</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-11.97973</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.05431</v>
-      </c>
-      <c r="I36" t="n">
-        <v>493</v>
-      </c>
-      <c r="J36" t="n">
-        <v>37</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-11.97973</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.05431</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>HUSARES DE JUNIN</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-11.97651</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.04822</v>
-      </c>
-      <c r="I37" t="n">
-        <v>352</v>
-      </c>
-      <c r="J37" t="n">
-        <v>16</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-11.97651</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.04822</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.00485</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-77.05274</v>
-      </c>
-      <c r="I38" t="n">
-        <v>18</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.00485</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-77.05274</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-11.97322</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-77.0474</v>
-      </c>
-      <c r="I39" t="n">
-        <v>240</v>
-      </c>
-      <c r="J39" t="n">
-        <v>11</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-11.97322</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-77.0474</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-11.9857</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-77.0543</v>
-      </c>
-      <c r="I40" t="n">
-        <v>240</v>
-      </c>
-      <c r="J40" t="n">
-        <v>15</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-11.9857</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-77.0543</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>SAN FRANCISCO SOLANO</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-11.9903</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-77.04825</v>
-      </c>
-      <c r="I41" t="n">
-        <v>225</v>
-      </c>
-      <c r="J41" t="n">
-        <v>12</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-11.9903</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-77.04825</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-11.99261</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-77.056</v>
-      </c>
-      <c r="I42" t="n">
-        <v>223</v>
-      </c>
-      <c r="J42" t="n">
-        <v>5</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-11.99261</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-77.056</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>MARIANO MELGAR</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-11.97291</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.04712000000001</v>
-      </c>
-      <c r="I43" t="n">
-        <v>393</v>
-      </c>
-      <c r="J43" t="n">
-        <v>24</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-11.97291</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.04712</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>3709 NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-11.98135</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-77.04949999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>728</v>
-      </c>
-      <c r="J44" t="n">
-        <v>39</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-11.98135</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-77.0495</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>SAN FRANCISCO DE ASIS SCHOOL</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.00963</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-77.05136</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.00963</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-77.05136</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>FRANKLIN ROOSEVELT</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-11.99906</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-77.04995</v>
-      </c>
-      <c r="I46" t="n">
-        <v>484</v>
-      </c>
-      <c r="J46" t="n">
-        <v>28</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-11.99906</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-77.04995</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>0009</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-11.9827</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-77.05979000000001</v>
-      </c>
-      <c r="I47" t="n">
-        <v>327</v>
-      </c>
-      <c r="J47" t="n">
-        <v>15</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-11.9827</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-77.05979</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>MESA REDONDA</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-12.00431</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-77.0574</v>
-      </c>
-      <c r="I48" t="n">
-        <v>378</v>
-      </c>
-      <c r="J48" t="n">
-        <v>20</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.00431</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-77.0574</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>2032 MANUEL SCORZA TORRES</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.0042</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-77.0564</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1063</v>
-      </c>
-      <c r="J49" t="n">
-        <v>52</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.0042</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-77.0564</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>2070 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-11.9839</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-77.06185000000001</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1182</v>
-      </c>
-      <c r="J50" t="n">
-        <v>57</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-11.9839</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-77.06185</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1182</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-11.98675</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-77.0596</v>
-      </c>
-      <c r="I51" t="n">
-        <v>266</v>
-      </c>
-      <c r="J51" t="n">
-        <v>19</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-11.98675</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-77.0596</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>MIGUEL ANGEL</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-11.98641</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-77.06052</v>
-      </c>
-      <c r="I52" t="n">
-        <v>300</v>
-      </c>
-      <c r="J52" t="n">
-        <v>25</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-11.98641</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-77.06052</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-11.97317</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-77.0475</v>
-      </c>
-      <c r="I53" t="n">
-        <v>288</v>
-      </c>
-      <c r="J53" t="n">
-        <v>18</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-11.97317</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-77.0475</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>JESUS EL BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-11.9864251387958</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-77.0559246570231</v>
-      </c>
-      <c r="I54" t="n">
-        <v>278</v>
-      </c>
-      <c r="J54" t="n">
-        <v>10</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-11.9864251387958</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-77.0559246570231</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>MILAGROSO SAN MARTIN</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-12.01012</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-77.05184</v>
-      </c>
-      <c r="I55" t="n">
-        <v>23</v>
-      </c>
-      <c r="J55" t="n">
-        <v>4</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-12.01012</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-77.05184</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>CATOLICA HIGH SCHOOL</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-11.98007</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-77.05656</v>
-      </c>
-      <c r="I56" t="n">
-        <v>357</v>
-      </c>
-      <c r="J56" t="n">
-        <v>11</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-11.98007</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-77.05656</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>TECHNOLOGY SCHOOLS DE INDEPENDENCIA</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-11.981897</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-77.048919</v>
-      </c>
-      <c r="I57" t="n">
-        <v>349</v>
-      </c>
-      <c r="J57" t="n">
-        <v>19</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-11.981897</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-77.048919</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>SAN IGNACIO DE INGENIERIA</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-11.983244</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-77.041113</v>
-      </c>
-      <c r="I58" t="n">
-        <v>279</v>
-      </c>
-      <c r="J58" t="n">
-        <v>13</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-11.983244</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-77.041113</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>CONSORCIO DEZA SCHOOL / GRUPO CIENTIFICO</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-11.97605</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-77.05271</v>
-      </c>
-      <c r="I59" t="n">
-        <v>730</v>
-      </c>
-      <c r="J59" t="n">
-        <v>17</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-11.97605</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-77.05271</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>SAN LUIS DE BORJA</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-11.9855</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-77.05295</v>
-      </c>
-      <c r="I60" t="n">
-        <v>524</v>
-      </c>
-      <c r="J60" t="n">
-        <v>17</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-11.9855</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-77.05295</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>JESUS EL BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-11.98697</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-77.05552</v>
-      </c>
-      <c r="I61" t="n">
-        <v>341</v>
-      </c>
-      <c r="J61" t="n">
-        <v>13</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-11.98697</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-77.05552</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>IZAGUIRRE DE ARIEL</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-12.00326</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-77.05318</v>
-      </c>
-      <c r="I62" t="n">
-        <v>259</v>
-      </c>
-      <c r="J62" t="n">
-        <v>18</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-12.00326</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-77.05318</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>LA CATOLICA</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-11.98027</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-77.05544</v>
-      </c>
-      <c r="I63" t="n">
-        <v>379</v>
-      </c>
-      <c r="J63" t="n">
-        <v>17</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-11.98027</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-77.05544</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>BAUTISTA LA LUZ</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-11.999386</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-77.042867</v>
-      </c>
-      <c r="I64" t="n">
-        <v>76</v>
-      </c>
-      <c r="J64" t="n">
-        <v>7</v>
-      </c>
-      <c r="K64" t="n">
-        <v>1</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-11.999386</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-77.042867</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-INDEPENDENCIA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-INDEPENDENCIA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>102471</t>
+          <t>306411</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA</t>
+          <t>SAN FRANCISCO DE ASIS SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.002377</t>
+          <t>-12.00963</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.053193</t>
+          <t>-77.05136</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>256576</t>
+          <t>598037</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MADRE TERESA DE CALCUTA</t>
+          <t>JESUS EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.999386</t>
+          <t>-11.9864251387958</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.042867</t>
+          <t>-77.0559246570231</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>278</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>305666</t>
+          <t>305925</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0007 EL ERMITAÑO</t>
+          <t>3049 IMPERIO DEL TAHUANTINSUYO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.9999</t>
+          <t>-11.9799</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.04992</t>
+          <t>-77.0367</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>305671</t>
+          <t>305690</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>09 J. WILLIAM FULBRIGHT / 3094-1 J. WILLIAM FULBRIGHT</t>
+          <t>0314</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.979</t>
+          <t>-11.97145</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.046</t>
+          <t>-77.04368</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>305685</t>
+          <t>305727</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0055 SAGRADO CORAZON DE JESUS</t>
+          <t>0385 JOSE OLAYA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.99997</t>
+          <t>-11.96767</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.05406</t>
+          <t>-77.03917</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>248</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,27 +811,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>305690</t>
+          <t>305751</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0314</t>
+          <t>0390-1 EL ERMITAÑO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.97145</t>
+          <t>-11.99921</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.04368</t>
+          <t>-77.04472</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>305713</t>
+          <t>306147</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0324 SAN JUDAS TADEO</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.9805</t>
+          <t>-11.97322</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.044</t>
+          <t>-77.0474</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,27 +935,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>305727</t>
+          <t>623621</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0385 JOSE OLAYA</t>
+          <t>CATOLICA HIGH SCHOOL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.96767</t>
+          <t>-11.98007</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.03917</t>
+          <t>-77.05656</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>357</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>305732</t>
+          <t>305968</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0386 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>3053 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.97702</t>
+          <t>-12.01675</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.05746</t>
+          <t>-77.0477</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>305751</t>
+          <t>306166</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0390-1 EL ERMITAÑO</t>
+          <t>SAN FRANCISCO SOLANO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.99921</t>
+          <t>-11.9903</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.04472</t>
+          <t>-77.04825</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>305770</t>
+          <t>305666</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0390-3 TAHUANTINSUYO</t>
+          <t>0007 EL ERMITAÑO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.9805</t>
+          <t>-11.9999</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.0403</t>
+          <t>-77.04992</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>319</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,42 +1183,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>305789</t>
+          <t>305713</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>0324 SAN JUDAS TADEO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.9975</t>
+          <t>-11.9805</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.0512</t>
+          <t>-77.044</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>298</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>305794</t>
+          <t>694642</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2044 VIRGEN DE FATIMA</t>
+          <t>SAN IGNACIO DE INGENIERIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.9908</t>
+          <t>-11.983244</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.0534</t>
+          <t>-77.041113</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>305807</t>
+          <t>698008</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2034 REPUBLICA DE IRLANDA</t>
+          <t>JESUS EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.99055</t>
+          <t>-11.98697</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.04115</t>
+          <t>-77.05552</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>341</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>305812</t>
+          <t>306152</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2036 MARIA AUXILIADORA</t>
+          <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.99068</t>
+          <t>-11.9857</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.04605</t>
+          <t>-77.0543</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>305826</t>
+          <t>332679</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2039 JORGE VICTOR CASTILLA MONTERO</t>
+          <t>0009</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.0003</t>
+          <t>-11.9827</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.0416</t>
+          <t>-77.05979</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>305831</t>
+          <t>305685</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2041 INCA GARCILASO DE LA VEGA</t>
+          <t>0055 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.96832</t>
+          <t>-11.99997</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.03948</t>
+          <t>-77.05406</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>324</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>305845</t>
+          <t>306072</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2052 MARIA AUXILIADORA</t>
+          <t>HUSARES DE JUNIN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.97215</t>
+          <t>-11.97651</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.05</t>
+          <t>-77.04822</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>352</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>305850</t>
+          <t>305732</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2053 FRANCISCO BOLOGNESI CERVANTES</t>
+          <t>0386 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.9906</t>
+          <t>-11.97702</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.0498</t>
+          <t>-77.05746</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>354</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>305869</t>
+          <t>695482</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2054 NUESTRA SEÑORA DE FATIMA</t>
+          <t>CONSORCIO DEZA SCHOOL / GRUPO CIENTIFICO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.00723</t>
+          <t>-11.97605</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.04978</t>
+          <t>-77.05271</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>730</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>305874</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2056 JOSE GALVEZ</t>
+          <t>SAN LUIS DE BORJA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.0062</t>
+          <t>-11.9855</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.0523</t>
+          <t>-77.05295</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>524</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>305888</t>
+          <t>698225</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2057 JOSE GABRIEL CONDORCANQUI</t>
+          <t>LA CATOLICA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.9715</t>
+          <t>-11.98027</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.0456</t>
+          <t>-77.05544</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>379</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>305893</t>
+          <t>575031</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2058 VIRGEN DE LA MEDALLA MILAGROSA</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.98001</t>
+          <t>-11.97317</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.04124</t>
+          <t>-77.0475</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>305906</t>
+          <t>698150</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2061 SAN MARTIN DE PORRES</t>
+          <t>IZAGUIRRE DE ARIEL</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.991217</t>
+          <t>-12.00326</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.052363</t>
+          <t>-77.05318</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>305911</t>
+          <t>335475</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>3048 SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.979157</t>
+          <t>-11.98675</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.053748</t>
+          <t>-77.0596</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>266</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>305925</t>
+          <t>647052</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3049 IMPERIO DEL TAHUANTINSUYO</t>
+          <t>TECHNOLOGY SCHOOLS DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.9799</t>
+          <t>-11.981897</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.0367</t>
+          <t>-77.048919</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>349</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>305930</t>
+          <t>332919</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3050 ALBERTO HURTADO ABADIA</t>
+          <t>MESA REDONDA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.99422</t>
+          <t>-12.00431</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.05423</t>
+          <t>-77.0574</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>378</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>305949</t>
+          <t>305770</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>0390-3 TAHUANTINSUYO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.00904</t>
+          <t>-11.9805</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.05035</t>
+          <t>-77.0403</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>344</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>305954</t>
+          <t>305807</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>2034 REPUBLICA DE IRLANDA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.0048</t>
+          <t>-11.99055</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.0509</t>
+          <t>-77.04115</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>439</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>305968</t>
+          <t>305812</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3053 VIRGEN DEL CARMEN</t>
+          <t>2036 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.01675</t>
+          <t>-11.99068</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.0477</t>
+          <t>-77.04605</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>474</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>305973</t>
+          <t>305794</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3056 GRAN BRETAÑA</t>
+          <t>2044 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.98067</t>
+          <t>-11.9908</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.04073</t>
+          <t>-77.0534</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>389</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>305987</t>
+          <t>305949</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3063 PATRICIA NATIVIDAD SANCHEZ</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-11.9989</t>
+          <t>-12.00904</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.0523</t>
+          <t>-77.05035</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>573</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>305992</t>
+          <t>306213</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3094 RAMIRO PRIALE PRIALE</t>
+          <t>MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.97711</t>
+          <t>-11.97291</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.05624</t>
+          <t>-77.04712</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>393</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>306005</t>
+          <t>335526</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>REPUBLICA DE COLOMBIA</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.98286</t>
+          <t>-11.98641</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.05382</t>
+          <t>-77.06052</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>306010</t>
+          <t>102471</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LIBERTADOR SAN MARTIN</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.97973</t>
+          <t>-12.002377</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.05431</t>
+          <t>-77.053193</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>456</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>306072</t>
+          <t>311785</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HUSARES DE JUNIN</t>
+          <t>FRANKLIN ROOSEVELT</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.97651</t>
+          <t>-11.99906</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.04822</t>
+          <t>-77.04995</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>484</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>306109</t>
+          <t>305869</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>2054 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.00485</t>
+          <t>-12.00723</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.05274</t>
+          <t>-77.04978</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>768</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>306147</t>
+          <t>306109</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.97322</t>
+          <t>-12.00485</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.0474</t>
+          <t>-77.05274</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>306152</t>
+          <t>305930</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PADUA</t>
+          <t>3050 ALBERTO HURTADO ABADIA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.9857</t>
+          <t>-11.99422</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.0543</t>
+          <t>-77.05423</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>792</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>306166</t>
+          <t>305874</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO SOLANO</t>
+          <t>2056 JOSE GALVEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.9903</t>
+          <t>-12.0062</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.04825</t>
+          <t>-77.0523</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>626</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>306171</t>
+          <t>305826</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>2039 JORGE VICTOR CASTILLA MONTERO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.99261</t>
+          <t>-12.0003</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.056</t>
+          <t>-77.0416</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>773</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>306213</t>
+          <t>305987</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MARIANO MELGAR</t>
+          <t>3063 PATRICIA NATIVIDAD SANCHEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.97291</t>
+          <t>-11.9989</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.04712</t>
+          <t>-77.0523</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>925</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>306350</t>
+          <t>306010</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3709 NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>LIBERTADOR SAN MARTIN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.98135</t>
+          <t>-11.97973</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.0495</t>
+          <t>-77.05431</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>493</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>306411</t>
+          <t>306350</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS SCHOOL</t>
+          <t>3709 NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.00963</t>
+          <t>-11.98135</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.05136</t>
+          <t>-77.0495</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>728</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>311785</t>
+          <t>256576</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FRANKLIN ROOSEVELT</t>
+          <t>MADRE TERESA DE CALCUTA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.99906</t>
+          <t>-11.999386</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.04995</t>
+          <t>-77.042867</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>332679</t>
+          <t>619426</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0009</t>
+          <t>MILAGROSO SAN MARTIN</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.9827</t>
+          <t>-12.01012</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.05979</t>
+          <t>-77.05184</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>332919</t>
+          <t>305992</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MESA REDONDA</t>
+          <t>3094 RAMIRO PRIALE PRIALE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.00431</t>
+          <t>-11.97711</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.0574</t>
+          <t>-77.05624</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>791</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>333136</t>
+          <t>305906</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2032 MANUEL SCORZA TORRES</t>
+          <t>2061 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.0042</t>
+          <t>-11.991217</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.0564</t>
+          <t>-77.052363</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>969</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,37 +3477,37 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>333160</t>
+          <t>305831</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2070 NUESTRA SEÑORA DEL CARMEN</t>
+          <t>2041 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-11.9839</t>
+          <t>-11.96832</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.06185</t>
+          <t>-77.03948</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>845</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>335475</t>
+          <t>305845</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU</t>
+          <t>2052 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-11.98675</t>
+          <t>-11.97215</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.0596</t>
+          <t>-77.05</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>805</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>335526</t>
+          <t>306171</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-11.98641</t>
+          <t>-11.99261</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.06052</t>
+          <t>-77.056</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>575031</t>
+          <t>305893</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>2058 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-11.97317</t>
+          <t>-11.98001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.0475</t>
+          <t>-77.04124</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>598037</t>
+          <t>333136</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JESUS EL BUEN PASTOR</t>
+          <t>2032 MANUEL SCORZA TORRES</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-11.9864251387958</t>
+          <t>-12.0042</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.0559246570231</t>
+          <t>-77.0564</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,37 +3787,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>619426</t>
+          <t>305954</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MILAGROSO SAN MARTIN</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.01012</t>
+          <t>-12.0048</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.05184</t>
+          <t>-77.0509</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>623621</t>
+          <t>333160</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CATOLICA HIGH SCHOOL</t>
+          <t>2070 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-11.98007</t>
+          <t>-11.9839</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.05656</t>
+          <t>-77.06185</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>647052</t>
+          <t>305671</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS DE INDEPENDENCIA</t>
+          <t>09 J. WILLIAM FULBRIGHT / 3094-1 J. WILLIAM FULBRIGHT</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-11.981897</t>
+          <t>-11.979</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.048919</t>
+          <t>-77.046</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3973,42 +3973,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>694642</t>
+          <t>305789</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE INGENIERIA</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-11.983244</t>
+          <t>-11.9975</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.041113</t>
+          <t>-77.0512</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>695482</t>
+          <t>305850</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CONSORCIO DEZA SCHOOL / GRUPO CIENTIFICO</t>
+          <t>2053 FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.97605</t>
+          <t>-11.9906</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.05271</t>
+          <t>-77.0498</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,37 +4097,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>857912</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SAN LUIS DE BORJA</t>
+          <t>BAUTISTA LA LUZ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.9855</t>
+          <t>-11.999386</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.05295</t>
+          <t>-77.042867</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>698008</t>
+          <t>305911</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JESUS EL BUEN PASTOR</t>
+          <t>3048 SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-11.98697</t>
+          <t>-11.979157</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.05552</t>
+          <t>-77.053748</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>698150</t>
+          <t>305973</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>IZAGUIRRE DE ARIEL</t>
+          <t>3056 GRAN BRETAÑA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-12.00326</t>
+          <t>-11.98067</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.05318</t>
+          <t>-77.04073</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>698225</t>
+          <t>305888</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LA CATOLICA</t>
+          <t>2057 JOSE GABRIEL CONDORCANQUI</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-11.98027</t>
+          <t>-11.9715</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.05544</t>
+          <t>-77.0456</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4345,37 +4345,37 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>857912</t>
+          <t>306005</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BAUTISTA LA LUZ</t>
+          <t>REPUBLICA DE COLOMBIA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-11.999386</t>
+          <t>-11.98286</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.042867</t>
+          <t>-77.05382</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>89</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-INDEPENDENCIA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-INDEPENDENCIA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>306411</t>
+          <t>857912</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DE ASIS SCHOOL</t>
+          <t>BAUTISTA LA LUZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.00963</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.05136</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.999386</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.042867</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>598037</t>
+          <t>698225</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JESUS EL BUEN PASTOR</t>
+          <t>LA CATOLICA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.9864251387958</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.0559246570231</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>-11.98027</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.05544</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>305925</t>
+          <t>698150</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3049 IMPERIO DEL TAHUANTINSUYO</t>
+          <t>IZAGUIRRE DE ARIEL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.9799</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.0367</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>-12.00326</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>-77.05318</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>305690</t>
+          <t>698008</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0314</t>
+          <t>JESUS EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.97145</t>
+          <t>341</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.04368</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-11.98697</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.05552</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>305727</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0385 JOSE OLAYA</t>
+          <t>SAN LUIS DE BORJA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.96767</t>
+          <t>524</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.03917</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>-11.9855</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.05295</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>305751</t>
+          <t>695482</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0390-1 EL ERMITAÑO</t>
+          <t>CONSORCIO DEZA SCHOOL / GRUPO CIENTIFICO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.99921</t>
+          <t>730</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.04472</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-11.97605</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.05271</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>306147</t>
+          <t>694642</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RICARDO PALMA</t>
+          <t>SAN IGNACIO DE INGENIERIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.97322</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.0474</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-11.983244</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.041113</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>623621</t>
+          <t>647052</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CATOLICA HIGH SCHOOL</t>
+          <t>TECHNOLOGY SCHOOLS DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.98007</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.05656</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>-11.981897</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.048919</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>305968</t>
+          <t>623621</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3053 VIRGEN DEL CARMEN</t>
+          <t>CATOLICA HIGH SCHOOL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.01675</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.0477</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-11.98007</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.05656</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>306166</t>
+          <t>619426</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO SOLANO</t>
+          <t>MILAGROSO SAN MARTIN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.9903</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.04825</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-12.01012</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.05184</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>305666</t>
+          <t>598037</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0007 EL ERMITAÑO</t>
+          <t>JESUS EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.9999</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.04992</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>-11.9864251387958</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.0559246570231</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>305713</t>
+          <t>575031</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0324 SAN JUDAS TADEO</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.9805</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.044</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>-11.97317</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.0475</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>694642</t>
+          <t>335526</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE INGENIERIA</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.983244</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.041113</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-11.98641</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.06052</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>698008</t>
+          <t>335475</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JESUS EL BUEN PASTOR</t>
+          <t>MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.98697</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.05552</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>-11.98675</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.0596</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>306152</t>
+          <t>333160</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PADUA</t>
+          <t>2070 NUESTRA SEÑORA DEL CARMEN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.9857</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.0543</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-11.9839</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.06185</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>332679</t>
+          <t>333136</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0009</t>
+          <t>2032 MANUEL SCORZA TORRES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.9827</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.05979</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>-12.0042</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.0564</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>305685</t>
+          <t>332919</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0055 SAGRADO CORAZON DE JESUS</t>
+          <t>MESA REDONDA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.99997</t>
+          <t>378</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.05406</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>-12.00431</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.0574</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>306072</t>
+          <t>332679</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HUSARES DE JUNIN</t>
+          <t>0009</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.97651</t>
+          <t>327</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.04822</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>-11.9827</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.05979</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>305732</t>
+          <t>311785</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0386 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>FRANKLIN ROOSEVELT</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.97702</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.05746</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>-11.99906</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.04995</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>695482</t>
+          <t>306411</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CONSORCIO DEZA SCHOOL / GRUPO CIENTIFICO</t>
+          <t>SAN FRANCISCO DE ASIS SCHOOL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.97605</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.05271</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>-12.00963</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.05136</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>306350</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAN LUIS DE BORJA</t>
+          <t>3709 NUESTRA SEÑORA DEL ROSARIO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.9855</t>
+          <t>728</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.05295</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>-11.98135</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.0495</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>698225</t>
+          <t>306213</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LA CATOLICA</t>
+          <t>MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.98027</t>
+          <t>393</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.05544</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>-11.97291</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.04712</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>575031</t>
+          <t>306171</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.97317</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.0475</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>-11.99261</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.056</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>698150</t>
+          <t>306166</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IZAGUIRRE DE ARIEL</t>
+          <t>SAN FRANCISCO SOLANO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.00326</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.05318</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-11.9903</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.04825</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>335475</t>
+          <t>306152</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU</t>
+          <t>SAN ANTONIO DE PADUA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.98675</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.0596</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>-11.9857</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.0543</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>647052</t>
+          <t>306147</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS DE INDEPENDENCIA</t>
+          <t>RICARDO PALMA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.981897</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.048919</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>-11.97322</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.0474</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>332919</t>
+          <t>306109</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MESA REDONDA</t>
+          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.00431</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.0574</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>-12.00485</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.05274</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>305770</t>
+          <t>306072</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0390-3 TAHUANTINSUYO</t>
+          <t>HUSARES DE JUNIN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.9805</t>
+          <t>352</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.0403</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>-11.97651</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.04822</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>305807</t>
+          <t>306010</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2034 REPUBLICA DE IRLANDA</t>
+          <t>LIBERTADOR SAN MARTIN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.99055</t>
+          <t>493</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.04115</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>-11.97973</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.05431</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>305812</t>
+          <t>306005</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2036 MARIA AUXILIADORA</t>
+          <t>REPUBLICA DE COLOMBIA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.99068</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.04605</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>-11.98286</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.05382</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>305794</t>
+          <t>305992</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2044 VIRGEN DE FATIMA</t>
+          <t>3094 RAMIRO PRIALE PRIALE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.9908</t>
+          <t>791</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.0534</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>-11.97711</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.05624</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>305949</t>
+          <t>305987</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3063 PATRICIA NATIVIDAD SANCHEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.00904</t>
+          <t>925</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.05035</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>-11.9989</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.0523</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>306213</t>
+          <t>305973</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MARIANO MELGAR</t>
+          <t>3056 GRAN BRETAÑA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.97291</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.04712</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>-11.98067</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.04073</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>335526</t>
+          <t>305968</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>3053 VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.98641</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.06052</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>-12.01675</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-77.0477</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>102471</t>
+          <t>305954</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.002377</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.053193</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>-12.0048</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.0509</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>311785</t>
+          <t>305949</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FRANKLIN ROOSEVELT</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.99906</t>
+          <t>573</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.04995</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>-12.00904</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.05035</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>305869</t>
+          <t>305930</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2054 NUESTRA SEÑORA DE FATIMA</t>
+          <t>3050 ALBERTO HURTADO ABADIA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.00723</t>
+          <t>792</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.04978</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>-11.99422</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.05423</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>306109</t>
+          <t>305925</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>3049 IMPERIO DEL TAHUANTINSUYO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.00485</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.05274</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-11.9799</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.0367</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>305930</t>
+          <t>305911</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3050 ALBERTO HURTADO ABADIA</t>
+          <t>3048 SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.99422</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.05423</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>-11.979157</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.053748</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>305874</t>
+          <t>305906</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2056 JOSE GALVEZ</t>
+          <t>2061 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.0062</t>
+          <t>969</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.0523</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>-11.991217</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.052363</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>305826</t>
+          <t>305893</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2039 JORGE VICTOR CASTILLA MONTERO</t>
+          <t>2058 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.0003</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.0416</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>-11.98001</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-77.04124</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>305987</t>
+          <t>305888</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3063 PATRICIA NATIVIDAD SANCHEZ</t>
+          <t>2057 JOSE GABRIEL CONDORCANQUI</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.9989</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.0523</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>-11.9715</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.0456</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>306010</t>
+          <t>305874</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LIBERTADOR SAN MARTIN</t>
+          <t>2056 JOSE GALVEZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.97973</t>
+          <t>626</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.05431</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>-12.0062</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.0523</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>306350</t>
+          <t>305869</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3709 NUESTRA SEÑORA DEL ROSARIO</t>
+          <t>2054 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.98135</t>
+          <t>768</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.0495</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>-12.00723</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.04978</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>256576</t>
+          <t>305850</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MADRE TERESA DE CALCUTA</t>
+          <t>2053 FRANCISCO BOLOGNESI CERVANTES</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.999386</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.042867</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-11.9906</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.0498</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3291,42 +3291,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>619426</t>
+          <t>305845</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MILAGROSO SAN MARTIN</t>
+          <t>2052 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.01012</t>
+          <t>805</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.05184</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-11.97215</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-77.05</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3353,37 +3353,37 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>305992</t>
+          <t>305831</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>3094 RAMIRO PRIALE PRIALE</t>
+          <t>2041 INCA GARCILASO DE LA VEGA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.97711</t>
+          <t>845</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.05624</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>-11.96832</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-77.03948</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>305906</t>
+          <t>305826</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2061 SAN MARTIN DE PORRES</t>
+          <t>2039 JORGE VICTOR CASTILLA MONTERO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.991217</t>
+          <t>773</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.052363</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>-12.0003</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-77.0416</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,37 +3477,37 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>305831</t>
+          <t>305812</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2041 INCA GARCILASO DE LA VEGA</t>
+          <t>2036 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-11.96832</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.03948</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>-11.99068</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-77.04605</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>305845</t>
+          <t>305807</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2052 MARIA AUXILIADORA</t>
+          <t>2034 REPUBLICA DE IRLANDA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-11.97215</t>
+          <t>439</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.05</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>-11.99055</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-77.04115</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>306171</t>
+          <t>305794</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>2044 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-11.99261</t>
+          <t>389</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.056</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>-11.9908</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-77.0534</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,37 +3663,37 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>305893</t>
+          <t>305789</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2058 VIRGEN DE LA MEDALLA MILAGROSA</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-11.98001</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.04124</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>-11.9975</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-77.0512</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>333136</t>
+          <t>305770</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2032 MANUEL SCORZA TORRES</t>
+          <t>0390-3 TAHUANTINSUYO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.0042</t>
+          <t>344</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.0564</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>-11.9805</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-77.0403</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3787,37 +3787,37 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>305954</t>
+          <t>305751</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>0390-1 EL ERMITAÑO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.0048</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.0509</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>-11.99921</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-77.04472</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>333160</t>
+          <t>305732</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2070 NUESTRA SEÑORA DEL CARMEN</t>
+          <t>0386 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-11.9839</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.06185</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>-11.97702</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-77.05746</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,42 +3911,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>305671</t>
+          <t>305727</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>09 J. WILLIAM FULBRIGHT / 3094-1 J. WILLIAM FULBRIGHT</t>
+          <t>0385 JOSE OLAYA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-11.979</t>
+          <t>248</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.046</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>-11.96767</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-77.03917</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3973,42 +3973,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>305789</t>
+          <t>305713</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>0324 SAN JUDAS TADEO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-11.9975</t>
+          <t>298</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.0512</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>-11.9805</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-77.044</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>305850</t>
+          <t>305690</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2053 FRANCISCO BOLOGNESI CERVANTES</t>
+          <t>0314</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.9906</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.0498</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>-11.97145</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-77.04368</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,37 +4097,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>857912</t>
+          <t>305685</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>BAUTISTA LA LUZ</t>
+          <t>0055 SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.999386</t>
+          <t>324</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.042867</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>-11.99997</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-77.05406</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>305911</t>
+          <t>305671</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>3048 SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>09 J. WILLIAM FULBRIGHT / 3094-1 J. WILLIAM FULBRIGHT</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-11.979157</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.053748</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>-11.979</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-77.046</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>305973</t>
+          <t>305666</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>3056 GRAN BRETAÑA</t>
+          <t>0007 EL ERMITAÑO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-11.98067</t>
+          <t>319</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.04073</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>-11.9999</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>-77.04992</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,42 +4283,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>305888</t>
+          <t>256576</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2057 JOSE GABRIEL CONDORCANQUI</t>
+          <t>MADRE TERESA DE CALCUTA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-11.9715</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.0456</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>-11.999386</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>-77.042867</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>306005</t>
+          <t>102471</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>REPUBLICA DE COLOMBIA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-11.98286</t>
+          <t>456</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.05382</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>-12.002377</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>-77.053193</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-INDEPENDENCIA.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-INDEPENDENCIA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
